--- a/server/master-excel-files/General_BIOLOGY_Grade 8.xlsx
+++ b/server/master-excel-files/General_BIOLOGY_Grade 8.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\BIOLOGY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -299,6 +299,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,11 +322,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -641,52 +641,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -828,7 +828,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -948,7 +948,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>6</v>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>6</v>
@@ -1014,7 +1014,7 @@
         <v>6</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>6</v>
@@ -1027,7 +1027,7 @@
       <c r="A13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1057,36 +1057,36 @@
       <c r="K13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="14"/>
-      <c r="AK13" s="14"/>
-      <c r="AL13" s="14"/>
-      <c r="AM13" s="14"/>
-      <c r="AN13" s="14"/>
-      <c r="AO13" s="14"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="8"/>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1102,9 +1102,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 E3:G13 H3:I47 J3:K13">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H13:I47 J13:K13 E13:G13">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K12">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
